--- a/feature/complement-spec-sos/ig/ValueSet-sas-valueset-categorieetablissement.xlsx
+++ b/feature/complement-spec-sos/ig/ValueSet-sas-valueset-categorieetablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:31:30+00:00</t>
+    <t>2026-09-10T12:57:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/complement-spec-sos/ig/ValueSet-sas-valueset-categorieetablissement.xlsx
+++ b/feature/complement-spec-sos/ig/ValueSet-sas-valueset-categorieetablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T12:57:05+00:00</t>
+    <t>2026-09-10T16:50:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/feature/complement-spec-sos/ig/ValueSet-sas-valueset-categorieetablissement.xlsx
+++ b/feature/complement-spec-sos/ig/ValueSet-sas-valueset-categorieetablissement.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-10T16:50:23+00:00</t>
+    <t>2026-09-11T12:15:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
